--- a/01_INPUTS/objccc.xlsx
+++ b/01_INPUTS/objccc.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Orbit\MATINAL_PENAFLOR\01_INPUTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A46211C4-EDB7-49D3-99CE-2EEFCAE86477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3F0281-1627-42B0-AA4E-33BE46B36109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{472D008F-7292-4943-B105-A39854C23553}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="total" sheetId="1" r:id="rId1"/>
+    <sheet name="autoservicio" sheetId="2" r:id="rId2"/>
+    <sheet name="tradicional" sheetId="3" r:id="rId3"/>
+    <sheet name="On premise" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="23">
   <si>
     <t>Canal</t>
   </si>
@@ -55,13 +58,61 @@
   </si>
   <si>
     <t>Objetivo CCC</t>
+  </si>
+  <si>
+    <t>MILAGROS ORTEGA</t>
+  </si>
+  <si>
+    <t>NADIA</t>
+  </si>
+  <si>
+    <t>GRIBAUDO ANGEL</t>
+  </si>
+  <si>
+    <t>PEYRONEL ANDREA</t>
+  </si>
+  <si>
+    <t>ALVAREZ VANESA</t>
+  </si>
+  <si>
+    <t>JOFRE GUILLERMO AGUSTIN</t>
+  </si>
+  <si>
+    <t>SANCHEZ FERNANDO JAVIER</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>V10</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>V6</t>
+  </si>
+  <si>
+    <t>V8</t>
+  </si>
+  <si>
+    <t>V7</t>
+  </si>
+  <si>
+    <t>V9</t>
+  </si>
+  <si>
+    <t>Empresa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,8 +128,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -97,8 +169,20 @@
         <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9DAF8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -156,11 +240,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -173,6 +332,30 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -546,4 +729,310 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB081E0-9AE7-4DAB-9890-F61695A71426}">
+  <dimension ref="A2:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="11"/>
+    <col min="2" max="2" width="28.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="12">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="9">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD47348-85A2-4C18-8DA4-92C2AF2609CC}">
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="28.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="6">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="14">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="14">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="14">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="14">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="14">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06FA2B96-E5F9-4515-B59B-7A1A903884DB}">
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="10">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="10">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/01_INPUTS/objccc.xlsx
+++ b/01_INPUTS/objccc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Orbit\MATINAL_PENAFLOR\01_INPUTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3F0281-1627-42B0-AA4E-33BE46B36109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FA06D1-6BCD-4EE6-AF0D-A8486C527187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{472D008F-7292-4943-B105-A39854C23553}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{472D008F-7292-4943-B105-A39854C23553}"/>
   </bookViews>
   <sheets>
     <sheet name="total" sheetId="1" r:id="rId1"/>
@@ -872,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="14">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -883,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="14">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -916,7 +916,7 @@
         <v>12</v>
       </c>
       <c r="D8" s="14">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -927,7 +927,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="14">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/01_INPUTS/objccc.xlsx
+++ b/01_INPUTS/objccc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Orbit\MATINAL_PENAFLOR\01_INPUTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FA06D1-6BCD-4EE6-AF0D-A8486C527187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF920486-CB0C-4954-99E7-680A14CDA110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{472D008F-7292-4943-B105-A39854C23553}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{472D008F-7292-4943-B105-A39854C23553}"/>
   </bookViews>
   <sheets>
     <sheet name="total" sheetId="1" r:id="rId1"/>
